--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="5" max="5"/>
@@ -975,7 +975,10 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="F16" s="2">
+        <f>D17*E17</f>
+        <v/>
+      </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
@@ -984,81 +987,6 @@
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="5" max="5"/>
@@ -461,7 +461,6 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="28.8" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -495,7 +494,6 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
     </row>
     <row r="3" ht="28.8" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -533,7 +531,6 @@
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
     </row>
     <row r="4" ht="28.8" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -567,7 +564,6 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
     </row>
     <row r="5" ht="28.8" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -601,155 +597,146 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
     </row>
     <row r="6" ht="28.8" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>keyboard</t>
+          <t>Monitor Arm</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APAC </t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>55</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F6" s="2">
-        <f>D6*E6</f>
+        <f>D8*E8</f>
         <v/>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46058</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>replaced faulty batch</t>
-        </is>
-      </c>
+        <v>46071</v>
+      </c>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
     </row>
     <row r="7" ht="28.8" customHeight="1">
       <c r="A7" s="2" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Monitor Arm</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t xml:space="preserve">APAC </t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>89.98999999999999</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2">
-        <f>D8*E8</f>
+        <f>D9*E9</f>
         <v/>
       </c>
       <c r="G7" s="3" t="n">
-        <v>46071</v>
+        <v>46084</v>
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
     </row>
     <row r="8" ht="28.8" customHeight="1">
       <c r="A8" s="2" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APAC </t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2">
-        <f>D9*E9</f>
+        <f>D10*E10</f>
         <v/>
       </c>
       <c r="G8" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2">
-        <f>D10*E10</f>
+        <f>D11*E11</f>
         <v/>
       </c>
       <c r="G9" s="3" t="n">
-        <v>46091</v>
+        <v>46096</v>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -758,235 +745,196 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="F10" s="2">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>46096</v>
-      </c>
-      <c r="H10" s="2" t="n"/>
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
     </row>
     <row r="11" ht="28.8" customHeight="1">
       <c r="A11" s="2" t="n">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>24.5</v>
+        <v>850</v>
       </c>
       <c r="F11" s="2">
-        <f>D12*E12</f>
+        <f>D13*E13</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>Urgent delivery</t>
         </is>
       </c>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>850</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2">
-        <f>D13*E13</f>
+        <f>D14*E14</f>
         <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Urgent delivery</t>
-        </is>
-      </c>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
     </row>
     <row r="13" ht="28.8" customHeight="1">
       <c r="A13" s="2" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="F13" s="2">
-        <f>D14*E14</f>
+        <f>D15*E15</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n"/>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
     </row>
     <row r="14" ht="43.2" customHeight="1">
       <c r="A14" s="2" t="n">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>190</v>
+        <v>25</v>
       </c>
       <c r="F14" s="2">
-        <f>D15*E15</f>
+        <f>D16*E16</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Standard shipping</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
     </row>
     <row r="15" ht="28.8" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>1016</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Keyboard</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>25</v>
-      </c>
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2">
-        <f>D16*E16</f>
-        <v/>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Standard shipping</t>
-        </is>
-      </c>
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="28.8" customHeight="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-    </row>
+    </row>
+    <row r="16" ht="28.8" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -139,6 +139,855 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Units by Product</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout/>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Units</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="1"/>
+          <cat>
+            <strRef>
+              <f>Sheet1!$B$2:$B$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="1">
+                  <v>USB-C Hub</v>
+                </pt>
+                <pt idx="2">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="3">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="4">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="5">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="6">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="7">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="8">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="9">
+                  <v>Laptop</v>
+                </pt>
+                <pt idx="10">
+                  <v>Headphones</v>
+                </pt>
+                <pt idx="11">
+                  <v>Monitor</v>
+                </pt>
+                <pt idx="12">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="13">
+                  <v>Webcam</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Sheet1!$D$2:$D$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>12</v>
+                </pt>
+                <pt idx="1">
+                  <v>30</v>
+                </pt>
+                <pt idx="2">
+                  <v>7</v>
+                </pt>
+                <pt idx="3">
+                  <v>25</v>
+                </pt>
+                <pt idx="4">
+                  <v>15</v>
+                </pt>
+                <pt idx="5">
+                  <v>22</v>
+                </pt>
+                <pt idx="6">
+                  <v>9</v>
+                </pt>
+                <pt idx="7">
+                  <v>18</v>
+                </pt>
+                <pt idx="8">
+                  <v>25</v>
+                </pt>
+                <pt idx="9">
+                  <v>12</v>
+                </pt>
+                <pt idx="10">
+                  <v>45</v>
+                </pt>
+                <pt idx="11">
+                  <v>20</v>
+                </pt>
+                <pt idx="12">
+                  <v>75</v>
+                </pt>
+                <pt idx="13">
+                  <v>5</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <layout/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Unit Price by Product</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout/>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$E$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Unit Price</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <strRef>
+              <f>Sheet1!$B$2:$B$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="1">
+                  <v>USB-C Hub</v>
+                </pt>
+                <pt idx="2">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="3">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="4">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="5">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="6">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="7">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="8">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="9">
+                  <v>Laptop</v>
+                </pt>
+                <pt idx="10">
+                  <v>Headphones</v>
+                </pt>
+                <pt idx="11">
+                  <v>Monitor</v>
+                </pt>
+                <pt idx="12">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="13">
+                  <v>Webcam</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Sheet1!$E$2:$E$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>24.5</v>
+                </pt>
+                <pt idx="1">
+                  <v>18</v>
+                </pt>
+                <pt idx="2">
+                  <v>89.98999999999999</v>
+                </pt>
+                <pt idx="3">
+                  <v>24.5</v>
+                </pt>
+                <pt idx="4">
+                  <v>89.98999999999999</v>
+                </pt>
+                <pt idx="5">
+                  <v>42</v>
+                </pt>
+                <pt idx="6">
+                  <v>55</v>
+                </pt>
+                <pt idx="7">
+                  <v>42</v>
+                </pt>
+                <pt idx="8">
+                  <v>24.5</v>
+                </pt>
+                <pt idx="9">
+                  <v>850</v>
+                </pt>
+                <pt idx="10">
+                  <v>60</v>
+                </pt>
+                <pt idx="11">
+                  <v>190</v>
+                </pt>
+                <pt idx="12">
+                  <v>25</v>
+                </pt>
+                <pt idx="13">
+                  <v>42</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <layout/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Units by Product</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout/>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Units</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="1"/>
+          <cat>
+            <strRef>
+              <f>Sheet1!$B$2:$B$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="1">
+                  <v>USB-C Hub</v>
+                </pt>
+                <pt idx="2">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="3">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="4">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="5">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="6">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="7">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="8">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="9">
+                  <v>Laptop</v>
+                </pt>
+                <pt idx="10">
+                  <v>Headphones</v>
+                </pt>
+                <pt idx="11">
+                  <v>Monitor</v>
+                </pt>
+                <pt idx="12">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="13">
+                  <v>Webcam</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Sheet1!$D$2:$D$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>12</v>
+                </pt>
+                <pt idx="1">
+                  <v>30</v>
+                </pt>
+                <pt idx="2">
+                  <v>7</v>
+                </pt>
+                <pt idx="3">
+                  <v>25</v>
+                </pt>
+                <pt idx="4">
+                  <v>15</v>
+                </pt>
+                <pt idx="5">
+                  <v>22</v>
+                </pt>
+                <pt idx="6">
+                  <v>9</v>
+                </pt>
+                <pt idx="7">
+                  <v>18</v>
+                </pt>
+                <pt idx="8">
+                  <v>25</v>
+                </pt>
+                <pt idx="9">
+                  <v>12</v>
+                </pt>
+                <pt idx="10">
+                  <v>45</v>
+                </pt>
+                <pt idx="11">
+                  <v>20</v>
+                </pt>
+                <pt idx="12">
+                  <v>75</v>
+                </pt>
+                <pt idx="13">
+                  <v>5</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <layout/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Unit Price by Product</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout/>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$E$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Unit Price</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <strRef>
+              <f>Sheet1!$B$2:$B$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="1">
+                  <v>USB-C Hub</v>
+                </pt>
+                <pt idx="2">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="3">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="4">
+                  <v>Monitor Arm</v>
+                </pt>
+                <pt idx="5">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="6">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="7">
+                  <v>Webcam</v>
+                </pt>
+                <pt idx="8">
+                  <v>Laptop Stand</v>
+                </pt>
+                <pt idx="9">
+                  <v>Laptop</v>
+                </pt>
+                <pt idx="10">
+                  <v>Headphones</v>
+                </pt>
+                <pt idx="11">
+                  <v>Monitor</v>
+                </pt>
+                <pt idx="12">
+                  <v>Keyboard</v>
+                </pt>
+                <pt idx="13">
+                  <v>Webcam</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Sheet1!$E$2:$E$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>24.5</v>
+                </pt>
+                <pt idx="1">
+                  <v>18</v>
+                </pt>
+                <pt idx="2">
+                  <v>89.98999999999999</v>
+                </pt>
+                <pt idx="3">
+                  <v>24.5</v>
+                </pt>
+                <pt idx="4">
+                  <v>89.98999999999999</v>
+                </pt>
+                <pt idx="5">
+                  <v>42</v>
+                </pt>
+                <pt idx="6">
+                  <v>55</v>
+                </pt>
+                <pt idx="7">
+                  <v>42</v>
+                </pt>
+                <pt idx="8">
+                  <v>24.5</v>
+                </pt>
+                <pt idx="9">
+                  <v>850</v>
+                </pt>
+                <pt idx="10">
+                  <v>60</v>
+                </pt>
+                <pt idx="11">
+                  <v>190</v>
+                </pt>
+                <pt idx="12">
+                  <v>25</v>
+                </pt>
+                <pt idx="13">
+                  <v>42</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <layout/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="5" max="5"/>
@@ -619,7 +1468,7 @@
         <v>89.98999999999999</v>
       </c>
       <c r="F6" s="2">
-        <f>D8*E8</f>
+        <f>D6*E6</f>
         <v/>
       </c>
       <c r="G6" s="3" t="n">
@@ -652,7 +1501,7 @@
         <v>42</v>
       </c>
       <c r="F7" s="2">
-        <f>D9*E9</f>
+        <f>D7*E7</f>
         <v/>
       </c>
       <c r="G7" s="3" t="n">
@@ -685,7 +1534,7 @@
         <v>55</v>
       </c>
       <c r="F8" s="2">
-        <f>D10*E10</f>
+        <f>D8*E8</f>
         <v/>
       </c>
       <c r="G8" s="3" t="n">
@@ -718,7 +1567,7 @@
         <v>42</v>
       </c>
       <c r="F9" s="2">
-        <f>D11*E11</f>
+        <f>D9*E9</f>
         <v/>
       </c>
       <c r="G9" s="3" t="n">
@@ -730,7 +1579,7 @@
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="28.8" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>1012</v>
       </c>
@@ -751,7 +1600,7 @@
         <v>24.5</v>
       </c>
       <c r="F10" s="2">
-        <f>D12*E12</f>
+        <f>D10*E10</f>
         <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -790,7 +1639,7 @@
         <v>850</v>
       </c>
       <c r="F11" s="2">
-        <f>D13*E13</f>
+        <f>D11*E11</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -808,7 +1657,7 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="28.8" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>1014</v>
       </c>
@@ -829,7 +1678,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="2">
-        <f>D14*E14</f>
+        <f>D12*E12</f>
         <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -864,7 +1713,7 @@
         <v>190</v>
       </c>
       <c r="F13" s="2">
-        <f>D15*E15</f>
+        <f>D13*E13</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -872,7 +1721,7 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
@@ -899,7 +1748,7 @@
         <v>25</v>
       </c>
       <c r="F14" s="2">
-        <f>D16*E16</f>
+        <f>D14*E14</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -918,25 +1767,63 @@
       <c r="L14" s="2" t="n"/>
     </row>
     <row r="15" ht="28.8" customHeight="1">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2">
-        <f>D17*E17</f>
+      <c r="A15" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Webcam</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>42</v>
+      </c>
+      <c r="F15">
+        <f>D15*E15</f>
         <v/>
       </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
     </row>
-    <row r="16" ht="28.8" customHeight="1"/>
+    <row r="16" ht="28.8" customHeight="1">
+      <c r="A16" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>KSA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -897,6 +897,88 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Units by Product</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sheet1'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$B$2:$B$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -982,6 +1064,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1306,7 +1410,11 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
@@ -1338,8 +1446,14 @@
       <c r="G2" s="3" t="n">
         <v>46036</v>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>top region</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -1376,7 +1490,9 @@
           <t>bulk order</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
+      <c r="I3" s="2" t="n">
+        <v>200</v>
+      </c>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>

--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Laptop case</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">

--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="5" max="5"/>
@@ -1907,36 +1907,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="28.8" customHeight="1">
-      <c r="A16" t="n">
-        <v>1018</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mouse</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>KSA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <f>D16*E16</f>
-        <v/>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
+    <row r="16" ht="28.8" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -979,6 +979,88 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Profit by Product</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sheet1'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$B$2:$B$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$I$2:$I$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1086,6 +1168,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
